--- a/docs/Mapping_casi_uso/cittadinanza/Citt_032.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_032.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="159">
   <si>
     <t>Sezione</t>
   </si>
@@ -315,6 +315,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>flag dichiarante</t>
@@ -541,7 +547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="16.73828125" customWidth="true" bestFit="true"/>
@@ -1619,7 +1625,7 @@
         <v>101</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>47</v>
@@ -1682,19 +1688,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1705,16 +1711,16 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>112</v>
@@ -1728,7 +1734,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>113</v>
@@ -1737,7 +1743,7 @@
         <v>9</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>114</v>
@@ -1751,7 +1757,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>115</v>
@@ -1760,7 +1766,7 @@
         <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>116</v>
@@ -1774,7 +1780,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>117</v>
@@ -1783,7 +1789,7 @@
         <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>118</v>
@@ -1797,7 +1803,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>119</v>
@@ -1806,7 +1812,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>120</v>
@@ -1820,7 +1826,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>121</v>
@@ -1829,10 +1835,10 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1843,19 +1849,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1866,19 +1872,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1889,19 +1895,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1912,7 +1918,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>127</v>
@@ -1921,7 +1927,7 @@
         <v>16</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>128</v>
@@ -1935,7 +1941,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>129</v>
@@ -1944,7 +1950,7 @@
         <v>16</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>130</v>
@@ -1958,16 +1964,16 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>132</v>
@@ -1981,19 +1987,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B63" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="C63" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2004,16 +2010,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>138</v>
@@ -2027,7 +2033,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>139</v>
@@ -2036,7 +2042,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>140</v>
@@ -2050,7 +2056,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>141</v>
@@ -2059,7 +2065,7 @@
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>142</v>
@@ -2073,7 +2079,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>143</v>
@@ -2082,7 +2088,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>144</v>
@@ -2096,16 +2102,16 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>146</v>
@@ -2119,7 +2125,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>147</v>
@@ -2128,7 +2134,7 @@
         <v>16</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>148</v>
@@ -2142,7 +2148,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>149</v>
@@ -2151,7 +2157,7 @@
         <v>16</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>150</v>
@@ -2165,7 +2171,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>151</v>
@@ -2174,13 +2180,13 @@
         <v>16</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>152</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>25</v>
@@ -2188,7 +2194,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>153</v>
@@ -2197,13 +2203,13 @@
         <v>16</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>154</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>25</v>
@@ -2211,7 +2217,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>155</v>
@@ -2220,7 +2226,7 @@
         <v>16</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>156</v>
@@ -2229,6 +2235,29 @@
         <v>10</v>
       </c>
       <c r="G73" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G74" s="2" t="s">
         <v>25</v>
       </c>
     </row>
